--- a/Data/Extension_Of_ENWR_Request.xlsx
+++ b/Data/Extension_Of_ENWR_Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DF6FA8-4A7C-471C-9056-CCEDA40B65F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE319BE-60FC-49D0-9884-F3B4813B33B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Data/Extension_Of_ENWR_Request.xlsx
+++ b/Data/Extension_Of_ENWR_Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE319BE-60FC-49D0-9884-F3B4813B33B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D6613-8CFC-44CD-935A-2A6E38952431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Instr_Slip_No</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>9012026A</t>
+  </si>
+  <si>
+    <t>shelflife_Days</t>
   </si>
 </sst>
 </file>
@@ -399,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -408,9 +411,10 @@
     <col min="4" max="4" width="25.140625" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -429,8 +433,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -449,38 +456,45 @@
       <c r="F2" s="4">
         <v>110001032504</v>
       </c>
+      <c r="G2" s="1">
+        <v>90</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Extension_Of_ENWR_Request.xlsx
+++ b/Data/Extension_Of_ENWR_Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D6613-8CFC-44CD-935A-2A6E38952431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A723DE2-179A-4388-A6B0-C900CAA8E0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Instr_Slip_No</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>ENWR</t>
-  </si>
-  <si>
-    <t>9012026A</t>
   </si>
   <si>
     <t>shelflife_Days</t>
@@ -58,7 +55,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +70,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -116,12 +119,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,30 +438,30 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
+      <c r="A2" s="1">
+        <v>70520261</v>
       </c>
       <c r="B2" s="1">
-        <v>9999996</v>
+        <v>6656413</v>
       </c>
       <c r="C2" s="1">
-        <v>1000421</v>
+        <v>6539191</v>
       </c>
       <c r="D2" s="3">
-        <v>100673000000011</v>
+        <v>120484000000134</v>
       </c>
       <c r="E2" s="1">
         <v>15</v>
       </c>
       <c r="F2" s="4">
-        <v>110001032504</v>
+        <v>110001509030</v>
       </c>
       <c r="G2" s="1">
-        <v>90</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -466,7 +470,9 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="F3" s="5">
+        <v>110001509014</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">

--- a/Data/Extension_Of_ENWR_Request.xlsx
+++ b/Data/Extension_Of_ENWR_Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A723DE2-179A-4388-A6B0-C900CAA8E0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A465C96A-F898-4B12-92CE-D98610A491A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,25 +443,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>70520261</v>
+        <v>4555604</v>
       </c>
       <c r="B2" s="1">
-        <v>6656413</v>
+        <v>9999996</v>
       </c>
       <c r="C2" s="1">
-        <v>6539191</v>
+        <v>1000421</v>
       </c>
       <c r="D2" s="3">
-        <v>120484000000134</v>
+        <v>100673000000011</v>
       </c>
       <c r="E2" s="1">
         <v>15</v>
       </c>
       <c r="F2" s="4">
-        <v>110001509030</v>
+        <v>110001042750</v>
       </c>
       <c r="G2" s="1">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
